--- a/src/时序数据预测-系列/单元时序预测-水质参数/TSM/data/样点13.xlsx
+++ b/src/时序数据预测-系列/单元时序预测-水质参数/TSM/data/样点13.xlsx
@@ -5,17 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\github_proj\Data-Miscellany-Forum\src\时序数据预测-系列\单元时序预测-水质参数\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\github_proj\Data-Miscellany-Forum\src\时序数据预测-系列\单元时序预测-水质参数\TSM\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304D793D-55DF-4761-A748-6E6B2747727A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D0B3C7-5985-4169-A327-D15FFA2E39D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="-15060" windowWidth="19425" windowHeight="10425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5220" yWindow="-11610" windowWidth="21600" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
@@ -49,10 +47,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="0.00000000000"/>
-    <numFmt numFmtId="179" formatCode="0.00000000_ "/>
+    <numFmt numFmtId="176" formatCode="0.00000000000"/>
+    <numFmt numFmtId="177" formatCode="0.00000000_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,13 +83,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -119,14 +110,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -399,11 +390,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="8" max="8" width="12.81640625"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1345,7 +1333,7 @@
         <v>5.6715621948242099</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>201910</v>
       </c>
@@ -1365,7 +1353,7 @@
         <v>5.7009797096252397</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>201911</v>
       </c>
@@ -1385,7 +1373,7 @@
         <v>5.9858613014221103</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>201912</v>
       </c>
@@ -1405,7 +1393,7 @@
         <v>5.9631156921386701</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>202001</v>
       </c>
@@ -1425,7 +1413,7 @@
         <v>5.7578210830688397</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>202002</v>
       </c>
@@ -1445,7 +1433,7 @@
         <v>5.7456755638122496</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>202003</v>
       </c>
@@ -1465,7 +1453,7 @@
         <v>6.0898666381835902</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>202004</v>
       </c>
@@ -1485,7 +1473,7 @@
         <v>6.3051404953002903</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>202005</v>
       </c>
@@ -1505,7 +1493,7 @@
         <v>5.6970863342285103</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>202006</v>
       </c>
@@ -1523,7 +1511,7 @@
         <v>4.9117150306701598</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>202007</v>
       </c>
@@ -1540,7 +1528,7 @@
         <v>4.6282162666320801</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>202008</v>
       </c>
@@ -1559,11 +1547,8 @@
       <c r="F59">
         <v>5.4974470138549796</v>
       </c>
-      <c r="H59" s="3">
-        <v>48.627352811800002</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>202009</v>
       </c>
@@ -1582,11 +1567,8 @@
       <c r="F60">
         <v>6.0908675193786603</v>
       </c>
-      <c r="H60" s="3">
-        <v>79.273907696199998</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>202010</v>
       </c>
@@ -1605,11 +1587,8 @@
       <c r="F61">
         <v>6.2515964508056596</v>
       </c>
-      <c r="H61" s="3">
-        <v>59.008130965600003</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>202011</v>
       </c>
@@ -1628,11 +1607,8 @@
       <c r="F62">
         <v>6.25514411926269</v>
       </c>
-      <c r="H62" s="3">
-        <v>50.067258450799997</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>202012</v>
       </c>
@@ -1651,11 +1627,8 @@
       <c r="F63">
         <v>6.9716215133666903</v>
       </c>
-      <c r="H63" s="3">
-        <v>50.2128028976</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>202101</v>
       </c>
@@ -2354,26 +2327,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
 </file>